--- a/test_doc/new_org/syllabus_6_science.xlsx
+++ b/test_doc/new_org/syllabus_6_science.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,16 +441,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Food: Where Does It Come From?</t>
+          <t>Living Organisms</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Food sources</t>
+          <t>Habitats</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -461,26 +461,26 @@
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>Plant and animal products</t>
+          <t>Adaptation</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Components of Food</t>
+          <t>Fibre to Fabric</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nutrients</t>
+          <t>Plant fibres</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>Balanced diet</t>
+          <t>Spinning and weaving</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -499,129 +499,129 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sorting Materials</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Deficiency diseases</t>
+          <t>Properties of materials</t>
         </is>
       </c>
       <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Term 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Grouping</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Food: Where Does It Come From?</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Food sources</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Term 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Plant and animal products</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Getting to Know Plants</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Parts of a plant</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Fibre to Fabric</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Plant fibres</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Term 1</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Spinning and weaving</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Sorting Materials</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Properties of materials</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Term 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Grouping</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2</v>
-      </c>
-    </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Separation of Substances</t>
-        </is>
-      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sieving and winnowing</t>
+          <t>Leaf, stem and root</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Term 1</t>
-        </is>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>Filtration and evaporation</t>
+          <t>Flower</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Changes Around Us</t>
+          <t>Light, Shadows and Reflections</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Reversible changes</t>
+          <t>Sources of light</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Term 1</t>
+          <t>Term 2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>Irreversible changes</t>
+          <t>Shadows</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -629,79 +629,79 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Getting to Know Plants</t>
-        </is>
-      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Parts of a plant</t>
+          <t>Reflection</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>3</v>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Term 2</t>
-        </is>
-      </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Body Movements</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Leaf, stem and root</t>
+          <t>Joints</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Term 2</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>Flower</t>
+          <t>Skeleton</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Body Movements</t>
-        </is>
-      </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Joints</t>
+          <t>Animal movement</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" t="inlineStr">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Electricity and Circuits</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Cells and bulbs</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>Term 2</t>
         </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Skeleton</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>Animal movement</t>
+          <t>Conductors and insulators</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -711,16 +711,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Living Organisms</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Habitats</t>
+          <t>Sources of water</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -731,26 +731,26 @@
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>Adaptation</t>
+          <t>Saving water</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Light, Shadows and Reflections</t>
+          <t>Components of Food</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sources of light</t>
+          <t>Nutrients</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -761,51 +761,21 @@
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>Shadows</t>
+          <t>Balanced diet</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>Reflection</t>
+          <t>Deficiency diseases</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Electricity and Circuits</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Cells and bulbs</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>4</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Term 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Conductors and insulators</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
